--- a/reports/FINAL_TEST_SUMMARY.xlsx
+++ b/reports/FINAL_TEST_SUMMARY.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated on 2026-08-29 12:46:09 after running all 4 testing suites</t>
+          <t>Generated on 2026-08-29 14:36:02 after running all 4 testing suites</t>
         </is>
       </c>
     </row>
